--- a/excel/C-Line.xlsx
+++ b/excel/C-Line.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ritar/Desktop/SP684-SupplierInfo/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09285ED2-9C56-8349-BEEC-6E91AA42617B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBEF80D5-FF8B-2C4E-8937-1CFCE5050005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{B65FD770-DD92-4482-9918-5A5A9EBC3770}"/>
+    <workbookView xWindow="2440" yWindow="600" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{B65FD770-DD92-4482-9918-5A5A9EBC3770}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Ref." sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="165">
   <si>
     <t>Internal Memo</t>
   </si>
@@ -108,40 +109,7 @@
     <t>ซีลายน์  7.0-7.5 กก.</t>
   </si>
   <si>
-    <t>ซีลายน์  7.6-7.9 กก.</t>
-  </si>
-  <si>
-    <t>ซีลายน์  8.0-8.5 กก.</t>
-  </si>
-  <si>
-    <t>ซีลายน์  9.0-9.5 กก.</t>
-  </si>
-  <si>
-    <t>ซีลายน์ 10.0-10.5 กก.</t>
-  </si>
-  <si>
     <t>1. โครงซีลายน์ - โรงงาน C&amp;T</t>
-  </si>
-  <si>
-    <t>ซีลายน์  5.3-5.5 กก.</t>
-  </si>
-  <si>
-    <t>ซีลายน์  5.6-5.8 กก.</t>
-  </si>
-  <si>
-    <t>ซีลายน์  6.2-6.4 กก.</t>
-  </si>
-  <si>
-    <t>ซีลายน์  6.5-6.7 กก.</t>
-  </si>
-  <si>
-    <t>ซีลายน์  7.1-7.3 กก.</t>
-  </si>
-  <si>
-    <t>ซีลายน์  7.7-7.9 กก.</t>
-  </si>
-  <si>
-    <t>ซีลายน์  8.0-8.2 กก.</t>
   </si>
   <si>
     <t>2. ฉากสังกะสี</t>
@@ -560,6 +528,96 @@
   <si>
     <t>1,2</t>
   </si>
+  <si>
+    <t>ทีรกร ซีลายน์  5.0-5.5 กก.</t>
+  </si>
+  <si>
+    <t>ทีรกร ซีลายน์  5.6-5.9 กก.</t>
+  </si>
+  <si>
+    <t>ทีรกร ซีลายน์  6.0-6.5 กก.</t>
+  </si>
+  <si>
+    <t>ทีรกร ซีลายน์  6.6-6.9 กก.</t>
+  </si>
+  <si>
+    <t>ทีรกร ซีลายน์  7.0-7.5 กก.</t>
+  </si>
+  <si>
+    <t>ทีรกร ซีลายน์  7.6-7.9 กก.</t>
+  </si>
+  <si>
+    <t>ทีรกร ซีลายน์  8.0-8.5 กก.</t>
+  </si>
+  <si>
+    <t>ทีรกร ซีลายน์  9.0-9.5 กก.</t>
+  </si>
+  <si>
+    <t>ทีรกร ซีลายน์ 10.0-10.5 กก.</t>
+  </si>
+  <si>
+    <t>C&amp;T ซีลายน์  5.3-5.5 กก.</t>
+  </si>
+  <si>
+    <t>C&amp;T ซีลายน์  5.6-5.8 กก.</t>
+  </si>
+  <si>
+    <t>C&amp;T ซีลายน์  6.2-6.4 กก.</t>
+  </si>
+  <si>
+    <t>C&amp;T ซีลายน์  6.5-6.7 กก.</t>
+  </si>
+  <si>
+    <t>C&amp;T ซีลายน์  7.1-7.3 กก.</t>
+  </si>
+  <si>
+    <t>C&amp;T ซีลายน์  7.7-7.9 กก.</t>
+  </si>
+  <si>
+    <t>C&amp;T ซีลายน์  8.0-8.2 กก.</t>
+  </si>
+  <si>
+    <t>C&amp;T ซีลายน์  9.0-9.5 กก.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ฉาก 2 รู (อมรชัย) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>** 3,000 ตัว/ลัง **</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ผ้าฉาบ (3 ม้วน/ห่อ) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>** 50 ห่อ/ลัง **</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ล็อคกิ้งคีย์ บาง (อมรชัย) ** 2,000 ตัว / ลัง** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ล็อคกิ้งคีย์ หนา (อมรชัย) ** 2,000 ตัว / ลัง** </t>
+  </si>
+  <si>
+    <t>ตะขอแขวน (อมรชัย) ** 2,000 ตัว/กระสอบ **</t>
+  </si>
 </sst>
 </file>
 
@@ -571,7 +629,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -800,6 +858,13 @@
     <font>
       <sz val="8"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1052,7 +1117,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -1388,7 +1453,24 @@
     <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1709,7 +1791,7 @@
   <dimension ref="A1:BR174"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="193" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8.6640625" customWidth="1"/>
     <col min="3" max="3" width="36.83203125" customWidth="1"/>
     <col min="4" max="5" width="8" customWidth="1"/>
@@ -1764,7 +1846,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="185"/>
@@ -1854,12 +1936,12 @@
       <c r="P8" s="4"/>
     </row>
     <row r="9" spans="1:70" s="6" customFormat="1" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="193"/>
+      <c r="A9"/>
       <c r="B9" s="23">
         <v>0.52500000000000002</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="26"/>
@@ -1950,12 +2032,12 @@
       <c r="BR9"/>
     </row>
     <row r="10" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="193"/>
+      <c r="A10"/>
       <c r="B10" s="23">
         <v>0.57499999999999996</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>19</v>
+        <v>144</v>
       </c>
       <c r="D10" s="36"/>
       <c r="E10" s="37"/>
@@ -2046,12 +2128,12 @@
       <c r="BR10"/>
     </row>
     <row r="11" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="193"/>
+      <c r="A11"/>
       <c r="B11" s="23">
         <v>0.625</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
@@ -2142,12 +2224,12 @@
       <c r="BR11"/>
     </row>
     <row r="12" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="193"/>
+      <c r="A12"/>
       <c r="B12" s="23">
         <v>0.67500000000000004</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="D12" s="36"/>
       <c r="E12" s="37"/>
@@ -2238,12 +2320,12 @@
       <c r="BR12"/>
     </row>
     <row r="13" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="193"/>
+      <c r="A13"/>
       <c r="B13" s="23">
         <v>0.72499999999999998</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="D13" s="36"/>
       <c r="E13" s="37"/>
@@ -2334,12 +2416,12 @@
       <c r="BR13"/>
     </row>
     <row r="14" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="193"/>
+      <c r="A14"/>
       <c r="B14" s="23">
         <v>0.77500000000000002</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="D14" s="36"/>
       <c r="E14" s="37"/>
@@ -2430,12 +2512,12 @@
       <c r="BR14"/>
     </row>
     <row r="15" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="193"/>
+      <c r="A15"/>
       <c r="B15" s="23">
         <v>0.82499999999999996</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="D15" s="36"/>
       <c r="E15" s="37"/>
@@ -2526,12 +2608,12 @@
       <c r="BR15"/>
     </row>
     <row r="16" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="193"/>
+      <c r="A16"/>
       <c r="B16" s="23">
         <v>0.92500000000000004</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D16" s="36"/>
       <c r="E16" s="37"/>
@@ -2622,12 +2704,12 @@
       <c r="BR16"/>
     </row>
     <row r="17" spans="1:70" s="6" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="193"/>
+      <c r="A17"/>
       <c r="B17" s="23">
         <v>1.0249999999999999</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="D17" s="44"/>
       <c r="E17" s="45"/>
@@ -2718,7 +2800,7 @@
       <c r="BR17"/>
     </row>
     <row r="18" spans="1:70" s="6" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="193"/>
+      <c r="A18"/>
       <c r="B18" s="23"/>
       <c r="C18" s="27"/>
       <c r="D18" s="50"/>
@@ -2795,7 +2877,7 @@
       </c>
       <c r="B19" s="18"/>
       <c r="C19" s="54" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D19" s="55"/>
       <c r="E19" s="56"/>
@@ -2810,12 +2892,12 @@
       <c r="N19" s="59"/>
     </row>
     <row r="20" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="193"/>
+      <c r="A20"/>
       <c r="B20" s="23">
         <v>0.54</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>28</v>
+        <v>152</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="26"/>
@@ -2906,12 +2988,12 @@
       <c r="BR20"/>
     </row>
     <row r="21" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="193"/>
+      <c r="A21"/>
       <c r="B21" s="23">
         <v>0.56999999999999995</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="D21" s="36"/>
       <c r="E21" s="37"/>
@@ -3002,12 +3084,12 @@
       <c r="BR21"/>
     </row>
     <row r="22" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="193"/>
+      <c r="A22"/>
       <c r="B22" s="23">
         <v>0.63</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>30</v>
+        <v>154</v>
       </c>
       <c r="D22" s="36"/>
       <c r="E22" s="37"/>
@@ -3098,12 +3180,12 @@
       <c r="BR22"/>
     </row>
     <row r="23" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="193"/>
+      <c r="A23"/>
       <c r="B23" s="23">
         <v>0.66</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>31</v>
+        <v>155</v>
       </c>
       <c r="D23" s="36"/>
       <c r="E23" s="37"/>
@@ -3194,12 +3276,12 @@
       <c r="BR23"/>
     </row>
     <row r="24" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="193"/>
+      <c r="A24"/>
       <c r="B24" s="23">
         <v>0.72</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="D24" s="36"/>
       <c r="E24" s="37"/>
@@ -3290,12 +3372,12 @@
       <c r="BR24"/>
     </row>
     <row r="25" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="193"/>
+      <c r="A25"/>
       <c r="B25" s="23">
         <v>0.78</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>33</v>
+        <v>157</v>
       </c>
       <c r="D25" s="36"/>
       <c r="E25" s="37"/>
@@ -3386,12 +3468,12 @@
       <c r="BR25"/>
     </row>
     <row r="26" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="193"/>
+      <c r="A26"/>
       <c r="B26" s="23">
         <v>0.81</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>34</v>
+        <v>158</v>
       </c>
       <c r="D26" s="36"/>
       <c r="E26" s="37"/>
@@ -3482,12 +3564,12 @@
       <c r="BR26"/>
     </row>
     <row r="27" spans="1:70" s="6" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="193"/>
+      <c r="A27"/>
       <c r="B27" s="23">
         <v>0.92500000000000004</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>25</v>
+        <v>159</v>
       </c>
       <c r="D27" s="44"/>
       <c r="E27" s="45"/>
@@ -3578,7 +3660,7 @@
       <c r="BR27"/>
     </row>
     <row r="28" spans="1:70" s="6" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="193"/>
+      <c r="A28"/>
       <c r="B28" s="62"/>
       <c r="C28"/>
       <c r="D28" s="32"/>
@@ -3652,7 +3734,7 @@
     <row r="29" spans="1:70" ht="22" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B29" s="64"/>
       <c r="C29" s="19" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="32"/>
@@ -3664,15 +3746,15 @@
       <c r="N29" s="32"/>
     </row>
     <row r="30" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A30" s="193">
+      <c r="A30">
         <f>_xlfn.XLOOKUP(Sheet1!B30,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>3</v>
       </c>
       <c r="B30" s="66" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C30" s="67" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D30" s="68"/>
       <c r="E30" s="69"/>
@@ -3707,15 +3789,15 @@
       </c>
     </row>
     <row r="31" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A31" s="193">
+      <c r="A31">
         <f>_xlfn.XLOOKUP(Sheet1!B31,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>3</v>
       </c>
       <c r="B31" s="66" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C31" s="75" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D31" s="76"/>
       <c r="E31" s="77"/>
@@ -3750,15 +3832,15 @@
       </c>
     </row>
     <row r="32" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A32" s="193">
+      <c r="A32">
         <f>_xlfn.XLOOKUP(Sheet1!B32,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>3</v>
       </c>
       <c r="B32" s="66" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C32" s="75" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D32" s="76"/>
       <c r="E32" s="77"/>
@@ -3793,7 +3875,7 @@
       </c>
     </row>
     <row r="33" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A33" s="193">
+      <c r="A33">
         <f>_xlfn.XLOOKUP(Sheet1!B33,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>1</v>
       </c>
@@ -3801,7 +3883,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D33" s="76"/>
       <c r="E33" s="77"/>
@@ -3836,7 +3918,7 @@
       </c>
     </row>
     <row r="34" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A34" s="193">
+      <c r="A34">
         <f>_xlfn.XLOOKUP(Sheet1!B34,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>1</v>
       </c>
@@ -3844,7 +3926,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="75" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D34" s="76"/>
       <c r="E34" s="77"/>
@@ -3879,7 +3961,7 @@
       </c>
     </row>
     <row r="35" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A35" s="193">
+      <c r="A35">
         <f>_xlfn.XLOOKUP(Sheet1!B35,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>2</v>
       </c>
@@ -3887,7 +3969,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="75" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D35" s="76"/>
       <c r="E35" s="77"/>
@@ -3922,7 +4004,7 @@
       </c>
     </row>
     <row r="36" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A36" s="193">
+      <c r="A36">
         <f>_xlfn.XLOOKUP(Sheet1!B36,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>2</v>
       </c>
@@ -3930,7 +4012,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="75" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D36" s="76"/>
       <c r="E36" s="77"/>
@@ -3965,7 +4047,7 @@
       </c>
     </row>
     <row r="37" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A37" s="193">
+      <c r="A37">
         <f>_xlfn.XLOOKUP(Sheet1!B37,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>2</v>
       </c>
@@ -3973,7 +4055,7 @@
         <v>3</v>
       </c>
       <c r="C37" s="75" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D37" s="76"/>
       <c r="E37" s="77"/>
@@ -4008,7 +4090,7 @@
       </c>
     </row>
     <row r="38" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A38" s="193">
+      <c r="A38">
         <f>_xlfn.XLOOKUP(Sheet1!B38,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>1</v>
       </c>
@@ -4016,7 +4098,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="84" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D38" s="85"/>
       <c r="E38" s="86"/>
@@ -4062,7 +4144,7 @@
       <c r="N39" s="32"/>
     </row>
     <row r="40" spans="1:70" s="6" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="193"/>
+      <c r="A40"/>
       <c r="B40" s="95"/>
       <c r="C40" s="96"/>
       <c r="D40" s="97"/>
@@ -4135,11 +4217,11 @@
     </row>
     <row r="41" spans="1:70" s="6" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B41" s="95"/>
       <c r="C41" s="100" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D41" s="32"/>
       <c r="E41" s="94"/>
@@ -4210,10 +4292,10 @@
       <c r="BR41"/>
     </row>
     <row r="42" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="193"/>
+      <c r="A42"/>
       <c r="B42" s="95"/>
       <c r="C42" s="103" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D42" s="68"/>
       <c r="E42" s="69"/>
@@ -4304,10 +4386,10 @@
       <c r="BR42"/>
     </row>
     <row r="43" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="193"/>
+      <c r="A43"/>
       <c r="B43" s="95"/>
       <c r="C43" s="106" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D43" s="76"/>
       <c r="E43" s="77"/>
@@ -4398,10 +4480,10 @@
       <c r="BR43"/>
     </row>
     <row r="44" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="193"/>
+      <c r="A44"/>
       <c r="B44" s="95"/>
       <c r="C44" s="106" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D44" s="76"/>
       <c r="E44" s="77"/>
@@ -4492,10 +4574,10 @@
       <c r="BR44"/>
     </row>
     <row r="45" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="193"/>
+      <c r="A45"/>
       <c r="B45" s="95"/>
       <c r="C45" s="106" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D45" s="76"/>
       <c r="E45" s="77"/>
@@ -4586,10 +4668,10 @@
       <c r="BR45"/>
     </row>
     <row r="46" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="193"/>
+      <c r="A46"/>
       <c r="B46" s="95"/>
       <c r="C46" s="106" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D46" s="76"/>
       <c r="E46" s="77"/>
@@ -4680,10 +4762,10 @@
       <c r="BR46"/>
     </row>
     <row r="47" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="193"/>
+      <c r="A47"/>
       <c r="B47" s="95"/>
       <c r="C47" s="106" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D47" s="76"/>
       <c r="E47" s="77"/>
@@ -4774,10 +4856,10 @@
       <c r="BR47"/>
     </row>
     <row r="48" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="193"/>
+      <c r="A48"/>
       <c r="B48" s="95"/>
       <c r="C48" s="106" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D48" s="76"/>
       <c r="E48" s="77"/>
@@ -4868,10 +4950,10 @@
       <c r="BR48"/>
     </row>
     <row r="49" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="193"/>
+      <c r="A49"/>
       <c r="B49" s="95"/>
       <c r="C49" s="106" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D49" s="76"/>
       <c r="E49" s="77"/>
@@ -4962,10 +5044,10 @@
       <c r="BR49"/>
     </row>
     <row r="50" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="193"/>
+      <c r="A50"/>
       <c r="B50" s="95"/>
       <c r="C50" s="106" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D50" s="76"/>
       <c r="E50" s="77"/>
@@ -5056,10 +5138,10 @@
       <c r="BR50"/>
     </row>
     <row r="51" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="193"/>
+      <c r="A51"/>
       <c r="B51" s="95"/>
       <c r="C51" s="106" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D51" s="76"/>
       <c r="E51" s="77"/>
@@ -5150,10 +5232,10 @@
       <c r="BR51"/>
     </row>
     <row r="52" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="193"/>
+      <c r="A52"/>
       <c r="B52" s="95"/>
       <c r="C52" s="106" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D52" s="76"/>
       <c r="E52" s="77"/>
@@ -5244,10 +5326,10 @@
       <c r="BR52"/>
     </row>
     <row r="53" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="193"/>
+      <c r="A53"/>
       <c r="B53" s="95"/>
       <c r="C53" s="106" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D53" s="76"/>
       <c r="E53" s="77"/>
@@ -5338,10 +5420,10 @@
       <c r="BR53"/>
     </row>
     <row r="54" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="193"/>
+      <c r="A54"/>
       <c r="B54" s="95"/>
       <c r="C54" s="106" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D54" s="76"/>
       <c r="E54" s="77"/>
@@ -5432,10 +5514,10 @@
       <c r="BR54"/>
     </row>
     <row r="55" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="193"/>
+      <c r="A55"/>
       <c r="B55" s="95"/>
       <c r="C55" s="106" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D55" s="76"/>
       <c r="E55" s="77"/>
@@ -5526,10 +5608,10 @@
       <c r="BR55"/>
     </row>
     <row r="56" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="193"/>
+      <c r="A56"/>
       <c r="B56" s="95"/>
       <c r="C56" s="106" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D56" s="76"/>
       <c r="E56" s="77"/>
@@ -5620,10 +5702,10 @@
       <c r="BR56"/>
     </row>
     <row r="57" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="193"/>
+      <c r="A57"/>
       <c r="B57" s="95"/>
       <c r="C57" s="106" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D57" s="76"/>
       <c r="E57" s="77"/>
@@ -5714,10 +5796,10 @@
       <c r="BR57"/>
     </row>
     <row r="58" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="193"/>
+      <c r="A58"/>
       <c r="B58" s="95"/>
       <c r="C58" s="106" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D58" s="76"/>
       <c r="E58" s="77"/>
@@ -5808,10 +5890,10 @@
       <c r="BR58"/>
     </row>
     <row r="59" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="193"/>
+      <c r="A59"/>
       <c r="B59" s="95"/>
       <c r="C59" s="106" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D59" s="76"/>
       <c r="E59" s="77"/>
@@ -5902,10 +5984,10 @@
       <c r="BR59"/>
     </row>
     <row r="60" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="193"/>
+      <c r="A60"/>
       <c r="B60" s="95"/>
       <c r="C60" s="106" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D60" s="76"/>
       <c r="E60" s="77"/>
@@ -5996,10 +6078,10 @@
       <c r="BR60"/>
     </row>
     <row r="61" spans="1:70" s="6" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="193"/>
+      <c r="A61"/>
       <c r="B61" s="95"/>
       <c r="C61" s="109" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D61" s="110"/>
       <c r="E61" s="111"/>
@@ -6090,7 +6172,7 @@
       <c r="BR61"/>
     </row>
     <row r="62" spans="1:70" s="6" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="193"/>
+      <c r="A62"/>
       <c r="B62" s="95"/>
       <c r="C62" s="96"/>
       <c r="D62" s="97"/>
@@ -6162,10 +6244,10 @@
       <c r="BR62"/>
     </row>
     <row r="63" spans="1:70" s="6" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="193"/>
+      <c r="A63"/>
       <c r="B63" s="95"/>
       <c r="C63" s="118" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D63" s="32"/>
       <c r="E63" s="94"/>
@@ -6236,10 +6318,10 @@
       <c r="BR63"/>
     </row>
     <row r="64" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="193"/>
+      <c r="A64"/>
       <c r="B64" s="95"/>
       <c r="C64" s="103" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D64" s="68"/>
       <c r="E64" s="69"/>
@@ -6330,10 +6412,10 @@
       <c r="BR64"/>
     </row>
     <row r="65" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="193"/>
+      <c r="A65"/>
       <c r="B65" s="95"/>
       <c r="C65" s="106" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D65" s="76"/>
       <c r="E65" s="77"/>
@@ -6424,10 +6506,10 @@
       <c r="BR65"/>
     </row>
     <row r="66" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="193"/>
+      <c r="A66"/>
       <c r="B66" s="95"/>
       <c r="C66" s="106" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D66" s="76"/>
       <c r="E66" s="77"/>
@@ -6518,10 +6600,10 @@
       <c r="BR66"/>
     </row>
     <row r="67" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="193"/>
+      <c r="A67"/>
       <c r="B67" s="95"/>
       <c r="C67" s="106" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D67" s="76"/>
       <c r="E67" s="77"/>
@@ -6612,10 +6694,10 @@
       <c r="BR67"/>
     </row>
     <row r="68" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="193"/>
+      <c r="A68"/>
       <c r="B68" s="95"/>
       <c r="C68" s="106" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D68" s="76"/>
       <c r="E68" s="77"/>
@@ -6706,10 +6788,10 @@
       <c r="BR68"/>
     </row>
     <row r="69" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="193"/>
+      <c r="A69"/>
       <c r="B69" s="95"/>
       <c r="C69" s="106" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D69" s="76"/>
       <c r="E69" s="77"/>
@@ -6800,10 +6882,10 @@
       <c r="BR69"/>
     </row>
     <row r="70" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="193"/>
+      <c r="A70"/>
       <c r="B70" s="95"/>
       <c r="C70" s="106" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D70" s="76"/>
       <c r="E70" s="77"/>
@@ -6894,10 +6976,10 @@
       <c r="BR70"/>
     </row>
     <row r="71" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="193"/>
+      <c r="A71"/>
       <c r="B71" s="95"/>
       <c r="C71" s="106" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D71" s="76"/>
       <c r="E71" s="77"/>
@@ -6988,10 +7070,10 @@
       <c r="BR71"/>
     </row>
     <row r="72" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="193"/>
+      <c r="A72"/>
       <c r="B72" s="95"/>
       <c r="C72" s="106" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D72" s="76"/>
       <c r="E72" s="77"/>
@@ -7082,10 +7164,10 @@
       <c r="BR72"/>
     </row>
     <row r="73" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="193"/>
+      <c r="A73"/>
       <c r="B73" s="95"/>
       <c r="C73" s="106" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D73" s="76"/>
       <c r="E73" s="77"/>
@@ -7176,10 +7258,10 @@
       <c r="BR73"/>
     </row>
     <row r="74" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="193"/>
+      <c r="A74"/>
       <c r="B74" s="95"/>
       <c r="C74" s="106" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D74" s="76"/>
       <c r="E74" s="77"/>
@@ -7270,10 +7352,10 @@
       <c r="BR74"/>
     </row>
     <row r="75" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="193"/>
+      <c r="A75"/>
       <c r="B75" s="95"/>
       <c r="C75" s="106" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D75" s="76"/>
       <c r="E75" s="77"/>
@@ -7364,10 +7446,10 @@
       <c r="BR75"/>
     </row>
     <row r="76" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="193"/>
+      <c r="A76"/>
       <c r="B76" s="95"/>
       <c r="C76" s="106" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D76" s="76"/>
       <c r="E76" s="77"/>
@@ -7458,10 +7540,10 @@
       <c r="BR76"/>
     </row>
     <row r="77" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="193"/>
+      <c r="A77"/>
       <c r="B77" s="95"/>
       <c r="C77" s="106" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D77" s="76"/>
       <c r="E77" s="77"/>
@@ -7552,10 +7634,10 @@
       <c r="BR77"/>
     </row>
     <row r="78" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="193"/>
+      <c r="A78"/>
       <c r="B78" s="95"/>
       <c r="C78" s="106" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D78" s="76"/>
       <c r="E78" s="77"/>
@@ -7646,10 +7728,10 @@
       <c r="BR78"/>
     </row>
     <row r="79" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="193"/>
+      <c r="A79"/>
       <c r="B79" s="95"/>
       <c r="C79" s="106" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D79" s="76"/>
       <c r="E79" s="77"/>
@@ -7740,10 +7822,10 @@
       <c r="BR79"/>
     </row>
     <row r="80" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="193"/>
+      <c r="A80"/>
       <c r="B80" s="95"/>
       <c r="C80" s="119" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D80" s="120"/>
       <c r="E80" s="121"/>
@@ -7834,10 +7916,10 @@
       <c r="BR80"/>
     </row>
     <row r="81" spans="1:70" s="6" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="193"/>
+      <c r="A81"/>
       <c r="B81" s="95"/>
       <c r="C81" s="127" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D81" s="128"/>
       <c r="E81" s="129"/>
@@ -7928,7 +8010,7 @@
       <c r="BR81"/>
     </row>
     <row r="82" spans="1:70" s="6" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="193"/>
+      <c r="A82"/>
       <c r="B82" s="95"/>
       <c r="C82" s="96"/>
       <c r="D82" s="97"/>
@@ -8002,7 +8084,7 @@
     <row r="83" spans="1:70" ht="22" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B83" s="95"/>
       <c r="C83" s="19" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="32"/>
@@ -8014,7 +8096,7 @@
       <c r="N83" s="102"/>
     </row>
     <row r="84" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A84" s="193">
+      <c r="A84">
         <f>_xlfn.XLOOKUP(Sheet1!B84,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>1</v>
       </c>
@@ -8022,7 +8104,7 @@
         <v>2</v>
       </c>
       <c r="C84" s="135" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D84" s="136"/>
       <c r="E84" s="137"/>
@@ -8049,7 +8131,7 @@
       </c>
     </row>
     <row r="85" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A85" s="193">
+      <c r="A85">
         <f>_xlfn.XLOOKUP(Sheet1!B85,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>2</v>
       </c>
@@ -8057,7 +8139,7 @@
         <v>3</v>
       </c>
       <c r="C85" s="144" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D85" s="76"/>
       <c r="E85" s="77"/>
@@ -8094,7 +8176,7 @@
     <row r="86" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B86" s="95"/>
       <c r="C86" s="145" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D86" s="146"/>
       <c r="E86" s="147"/>
@@ -8110,7 +8192,7 @@
     <row r="87" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B87" s="95"/>
       <c r="C87" s="145" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D87" s="146"/>
       <c r="E87" s="147"/>
@@ -8126,7 +8208,7 @@
     <row r="88" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B88" s="95"/>
       <c r="C88" s="145" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D88" s="146"/>
       <c r="E88" s="147"/>
@@ -8140,7 +8222,7 @@
       <c r="N88" s="149"/>
     </row>
     <row r="89" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A89" s="193">
+      <c r="A89">
         <f>_xlfn.XLOOKUP(Sheet1!B89,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>1</v>
       </c>
@@ -8148,7 +8230,7 @@
         <v>2</v>
       </c>
       <c r="C89" s="145" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D89" s="120"/>
       <c r="E89" s="121"/>
@@ -8174,7 +8256,7 @@
       </c>
     </row>
     <row r="90" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A90" s="193">
+      <c r="A90">
         <f>_xlfn.XLOOKUP(Sheet1!B90,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>2</v>
       </c>
@@ -8182,7 +8264,7 @@
         <v>3</v>
       </c>
       <c r="C90" s="144" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D90" s="76"/>
       <c r="E90" s="77"/>
@@ -8219,7 +8301,7 @@
     <row r="91" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B91" s="95"/>
       <c r="C91" s="145" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D91" s="146"/>
       <c r="E91" s="147"/>
@@ -8235,7 +8317,7 @@
     <row r="92" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B92" s="95"/>
       <c r="C92" s="145" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D92" s="146"/>
       <c r="E92" s="147"/>
@@ -8251,7 +8333,7 @@
     <row r="93" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B93" s="95"/>
       <c r="C93" s="145" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D93" s="146"/>
       <c r="E93" s="147"/>
@@ -8265,7 +8347,7 @@
       <c r="N93" s="149"/>
     </row>
     <row r="94" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A94" s="193">
+      <c r="A94">
         <f>_xlfn.XLOOKUP(Sheet1!B94,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>1</v>
       </c>
@@ -8273,7 +8355,7 @@
         <v>2</v>
       </c>
       <c r="C94" s="145" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D94" s="120"/>
       <c r="E94" s="121"/>
@@ -8299,7 +8381,7 @@
       </c>
     </row>
     <row r="95" spans="1:70" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="193">
+      <c r="A95">
         <f>_xlfn.XLOOKUP(Sheet1!B95,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9)</f>
         <v>2</v>
       </c>
@@ -8307,7 +8389,7 @@
         <v>3</v>
       </c>
       <c r="C95" s="150" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D95" s="110"/>
       <c r="E95" s="111"/>
@@ -8357,7 +8439,7 @@
     <row r="97" spans="2:14" ht="22" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B97" s="95"/>
       <c r="C97" s="19" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D97" s="65"/>
       <c r="E97" s="32"/>
@@ -8373,7 +8455,7 @@
     <row r="98" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B98" s="95"/>
       <c r="C98" s="153" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D98" s="154"/>
       <c r="E98" s="155"/>
@@ -8401,7 +8483,7 @@
     <row r="99" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B99" s="95"/>
       <c r="C99" s="145" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D99" s="120"/>
       <c r="E99" s="147"/>
@@ -8429,7 +8511,7 @@
     <row r="100" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B100" s="95"/>
       <c r="C100" s="145" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D100" s="120"/>
       <c r="E100" s="147"/>
@@ -8457,7 +8539,7 @@
     <row r="101" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B101" s="95"/>
       <c r="C101" s="145" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D101" s="120"/>
       <c r="E101" s="147"/>
@@ -8485,7 +8567,7 @@
     <row r="102" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B102" s="95"/>
       <c r="C102" s="161" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D102" s="128"/>
       <c r="E102" s="129"/>
@@ -8527,7 +8609,7 @@
     <row r="104" spans="2:14" ht="22" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B104" s="95"/>
       <c r="C104" s="162" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D104" s="65"/>
       <c r="E104" s="32"/>
@@ -8543,7 +8625,7 @@
     <row r="105" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B105" s="95"/>
       <c r="C105" s="153" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D105" s="154"/>
       <c r="E105" s="155"/>
@@ -8571,7 +8653,7 @@
     <row r="106" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B106" s="95"/>
       <c r="C106" s="145" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D106" s="120"/>
       <c r="E106" s="147"/>
@@ -8599,7 +8681,7 @@
     <row r="107" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B107" s="95"/>
       <c r="C107" s="161" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D107" s="128"/>
       <c r="E107" s="163"/>
@@ -8641,7 +8723,7 @@
     <row r="109" spans="2:14" ht="22" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B109" s="95"/>
       <c r="C109" s="100" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D109" s="65"/>
       <c r="E109" s="32"/>
@@ -8657,7 +8739,7 @@
     <row r="110" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B110" s="95"/>
       <c r="C110" s="153" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D110" s="154">
         <f>E110/1.07</f>
@@ -8690,7 +8772,7 @@
     <row r="111" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B111" s="95"/>
       <c r="C111" s="145" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D111" s="120">
         <f t="shared" ref="D111:D112" si="44">E111/1.07</f>
@@ -8723,7 +8805,7 @@
     <row r="112" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B112" s="95"/>
       <c r="C112" s="161" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D112" s="128">
         <f t="shared" si="44"/>
@@ -8756,7 +8838,7 @@
     <row r="113" spans="1:14" ht="22" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B113" s="95"/>
       <c r="C113" s="165" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D113" s="65"/>
       <c r="E113" s="32"/>
@@ -8768,7 +8850,7 @@
       <c r="N113" s="102"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A114" s="193">
+      <c r="A114">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B114,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>1</v>
       </c>
@@ -8776,7 +8858,7 @@
         <v>2</v>
       </c>
       <c r="C114" s="167" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D114" s="25"/>
       <c r="E114" s="26"/>
@@ -8811,7 +8893,7 @@
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A115" s="193">
+      <c r="A115">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B115,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>1</v>
       </c>
@@ -8819,7 +8901,7 @@
         <v>2</v>
       </c>
       <c r="C115" s="170" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D115" s="36"/>
       <c r="E115" s="37"/>
@@ -8854,7 +8936,7 @@
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A116" s="193">
+      <c r="A116">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B116,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>2</v>
       </c>
@@ -8862,7 +8944,7 @@
         <v>3</v>
       </c>
       <c r="C116" s="170" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D116" s="36"/>
       <c r="E116" s="37"/>
@@ -8897,15 +8979,15 @@
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A117" s="193">
+      <c r="A117">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B117,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>3</v>
       </c>
       <c r="B117" s="174" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C117" s="170" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D117" s="36"/>
       <c r="E117" s="37"/>
@@ -8940,13 +9022,13 @@
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A118" s="193" t="str">
+      <c r="A118" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B118,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B118" s="174"/>
       <c r="C118" s="170" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D118" s="36"/>
       <c r="E118" s="37"/>
@@ -8981,15 +9063,15 @@
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A119" s="193">
+      <c r="A119">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B119,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>4</v>
       </c>
       <c r="B119" s="175" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C119" s="170" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D119" s="36"/>
       <c r="E119" s="37"/>
@@ -9024,13 +9106,13 @@
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A120" s="193" t="str">
+      <c r="A120" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B120,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B120" s="166"/>
       <c r="C120" s="170" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D120" s="36"/>
       <c r="E120" s="37"/>
@@ -9065,7 +9147,7 @@
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A121" s="193">
+      <c r="A121">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B121,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>1</v>
       </c>
@@ -9073,7 +9155,7 @@
         <v>2</v>
       </c>
       <c r="C121" s="170" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D121" s="36"/>
       <c r="E121" s="37"/>
@@ -9108,7 +9190,7 @@
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A122" s="193">
+      <c r="A122">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B122,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>2</v>
       </c>
@@ -9116,7 +9198,7 @@
         <v>3</v>
       </c>
       <c r="C122" s="170" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D122" s="36"/>
       <c r="E122" s="37"/>
@@ -9151,15 +9233,15 @@
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A123" s="193">
+      <c r="A123">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B123,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>3</v>
       </c>
       <c r="B123" s="174" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C123" s="170" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D123" s="36"/>
       <c r="E123" s="37"/>
@@ -9194,15 +9276,15 @@
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A124" s="193">
+      <c r="A124">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B124,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>4</v>
       </c>
       <c r="B124" s="178" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C124" s="170" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D124" s="36"/>
       <c r="E124" s="37"/>
@@ -9237,7 +9319,7 @@
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A125" s="193">
+      <c r="A125">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B125,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>1</v>
       </c>
@@ -9245,7 +9327,7 @@
         <v>2</v>
       </c>
       <c r="C125" s="170" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D125" s="36"/>
       <c r="E125" s="37"/>
@@ -9280,15 +9362,15 @@
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A126" s="193">
+      <c r="A126">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B126,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>3</v>
       </c>
       <c r="B126" s="174" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C126" s="170" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D126" s="36"/>
       <c r="E126" s="37"/>
@@ -9323,7 +9405,7 @@
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A127" s="193">
+      <c r="A127">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B127,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>2</v>
       </c>
@@ -9331,7 +9413,7 @@
         <v>3</v>
       </c>
       <c r="C127" s="170" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D127" s="36"/>
       <c r="E127" s="37"/>
@@ -9366,15 +9448,15 @@
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A128" s="193">
+      <c r="A128">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B128,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>4</v>
       </c>
       <c r="B128" s="178" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C128" s="170" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D128" s="36"/>
       <c r="E128" s="37"/>
@@ -9409,15 +9491,15 @@
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A129" s="193">
+      <c r="A129">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B129,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>1</v>
       </c>
       <c r="B129" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="C129" s="170" t="s">
-        <v>104</v>
+      <c r="C129" s="198" t="s">
+        <v>93</v>
       </c>
       <c r="D129" s="36"/>
       <c r="E129" s="37"/>
@@ -9452,15 +9534,15 @@
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A130" s="193">
+      <c r="A130">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B130,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>1</v>
       </c>
       <c r="B130" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="C130" s="170" t="s">
-        <v>105</v>
+      <c r="C130" s="198" t="s">
+        <v>94</v>
       </c>
       <c r="D130" s="36"/>
       <c r="E130" s="37"/>
@@ -9495,15 +9577,15 @@
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A131" s="193">
+      <c r="A131">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B131,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>2</v>
       </c>
       <c r="B131" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="C131" s="170" t="s">
-        <v>106</v>
+      <c r="C131" s="198" t="s">
+        <v>95</v>
       </c>
       <c r="D131" s="36"/>
       <c r="E131" s="37"/>
@@ -9538,15 +9620,15 @@
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A132" s="193">
+      <c r="A132">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B132,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>2</v>
       </c>
       <c r="B132" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="C132" s="170" t="s">
-        <v>107</v>
+      <c r="C132" s="198" t="s">
+        <v>96</v>
       </c>
       <c r="D132" s="36"/>
       <c r="E132" s="37"/>
@@ -9581,15 +9663,15 @@
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A133" s="193">
+      <c r="A133">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B133,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>3</v>
       </c>
       <c r="B133" s="174" t="s">
-        <v>36</v>
-      </c>
-      <c r="C133" s="170" t="s">
-        <v>108</v>
+        <v>25</v>
+      </c>
+      <c r="C133" s="198" t="s">
+        <v>97</v>
       </c>
       <c r="D133" s="36"/>
       <c r="E133" s="37"/>
@@ -9624,13 +9706,13 @@
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A134" s="193" t="str">
+      <c r="A134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B134,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B134" s="175"/>
-      <c r="C134" s="170" t="s">
-        <v>109</v>
+      <c r="C134" s="198" t="s">
+        <v>98</v>
       </c>
       <c r="D134" s="36"/>
       <c r="E134" s="37"/>
@@ -9665,15 +9747,15 @@
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A135" s="193">
+      <c r="A135">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B135,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>1</v>
       </c>
       <c r="B135" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="C135" s="170" t="s">
-        <v>110</v>
+      <c r="C135" s="198" t="s">
+        <v>99</v>
       </c>
       <c r="D135" s="36"/>
       <c r="E135" s="37"/>
@@ -9708,15 +9790,15 @@
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A136" s="193">
+      <c r="A136">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B136,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>2</v>
       </c>
       <c r="B136" s="173" t="s">
         <v>3</v>
       </c>
-      <c r="C136" s="170" t="s">
-        <v>111</v>
+      <c r="C136" s="198" t="s">
+        <v>100</v>
       </c>
       <c r="D136" s="36"/>
       <c r="E136" s="37"/>
@@ -9751,15 +9833,15 @@
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A137" s="193">
+      <c r="A137">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B137,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>3</v>
       </c>
       <c r="B137" s="174" t="s">
-        <v>36</v>
-      </c>
-      <c r="C137" s="170" t="s">
-        <v>112</v>
+        <v>25</v>
+      </c>
+      <c r="C137" s="198" t="s">
+        <v>101</v>
       </c>
       <c r="D137" s="36"/>
       <c r="E137" s="37"/>
@@ -9794,13 +9876,13 @@
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A138" s="193" t="str">
+      <c r="A138" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B138,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B138" s="175"/>
       <c r="C138" s="170" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D138" s="36"/>
       <c r="E138" s="37"/>
@@ -9835,13 +9917,13 @@
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A139" s="193" t="str">
+      <c r="A139" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B139,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B139" s="175"/>
       <c r="C139" s="170" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D139" s="36"/>
       <c r="E139" s="37"/>
@@ -9876,15 +9958,15 @@
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A140" s="193">
+      <c r="A140">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B140,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>4</v>
       </c>
       <c r="B140" s="175" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C140" s="170" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D140" s="36"/>
       <c r="E140" s="37"/>
@@ -9919,15 +10001,15 @@
       </c>
     </row>
     <row r="141" spans="1:14" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="193">
+      <c r="A141">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B141,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>6</v>
       </c>
       <c r="B141" s="179" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C141" s="170" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D141" s="36"/>
       <c r="E141" s="37"/>
@@ -9961,15 +10043,15 @@
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A142" s="193">
+      <c r="A142">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B142,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>3</v>
       </c>
       <c r="B142" s="174" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C142" s="170" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D142" s="36"/>
       <c r="E142" s="37"/>
@@ -10004,7 +10086,7 @@
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A143" s="193">
+      <c r="A143">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B143,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>1</v>
       </c>
@@ -10012,7 +10094,7 @@
         <v>2</v>
       </c>
       <c r="C143" s="170" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D143" s="36"/>
       <c r="E143" s="37"/>
@@ -10047,15 +10129,15 @@
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A144" s="193">
+      <c r="A144">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B144,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>5</v>
       </c>
       <c r="B144" s="175" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C144" s="170" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D144" s="36"/>
       <c r="E144" s="37"/>
@@ -10090,13 +10172,13 @@
       </c>
     </row>
     <row r="145" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A145" s="193" t="str">
+      <c r="A145" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B145,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B145" s="175"/>
       <c r="C145" s="170" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D145" s="36"/>
       <c r="E145" s="37"/>
@@ -10131,13 +10213,13 @@
       </c>
     </row>
     <row r="146" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A146" s="193" t="str">
+      <c r="A146" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B146,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B146" s="175"/>
       <c r="C146" s="170" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D146" s="36"/>
       <c r="E146" s="37"/>
@@ -10172,15 +10254,15 @@
       </c>
     </row>
     <row r="147" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="193">
+      <c r="A147">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B147,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>7</v>
       </c>
       <c r="B147" s="175" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C147" s="170" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D147" s="36"/>
       <c r="E147" s="37"/>
@@ -10271,15 +10353,15 @@
       <c r="BR147"/>
     </row>
     <row r="148" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="193">
+      <c r="A148">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B148,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>7</v>
       </c>
       <c r="B148" s="175" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C148" s="170" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D148" s="36"/>
       <c r="E148" s="37"/>
@@ -10370,15 +10452,15 @@
       <c r="BR148"/>
     </row>
     <row r="149" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="193">
+      <c r="A149">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B149,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>7</v>
       </c>
       <c r="B149" s="175" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C149" s="170" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D149" s="36"/>
       <c r="E149" s="37"/>
@@ -10469,7 +10551,7 @@
       <c r="BR149"/>
     </row>
     <row r="150" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="193">
+      <c r="A150">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B150,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>1</v>
       </c>
@@ -10477,7 +10559,7 @@
         <v>2</v>
       </c>
       <c r="C150" s="170" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D150" s="36"/>
       <c r="E150" s="37"/>
@@ -10568,15 +10650,15 @@
       <c r="BR150"/>
     </row>
     <row r="151" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="193">
+      <c r="A151">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B151,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>7</v>
       </c>
       <c r="B151" s="175" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C151" s="170" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D151" s="36"/>
       <c r="E151" s="37"/>
@@ -10667,15 +10749,15 @@
       <c r="BR151"/>
     </row>
     <row r="152" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="193">
+      <c r="A152">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B152,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>7</v>
       </c>
       <c r="B152" s="175" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C152" s="170" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D152" s="36"/>
       <c r="E152" s="37"/>
@@ -10766,15 +10848,15 @@
       <c r="BR152"/>
     </row>
     <row r="153" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="193">
+      <c r="A153">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B153,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>7</v>
       </c>
       <c r="B153" s="175" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C153" s="170" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D153" s="36"/>
       <c r="E153" s="37"/>
@@ -10865,7 +10947,7 @@
       <c r="BR153"/>
     </row>
     <row r="154" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="193">
+      <c r="A154">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B154,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>1</v>
       </c>
@@ -10873,7 +10955,7 @@
         <v>2</v>
       </c>
       <c r="C154" s="170" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D154" s="36"/>
       <c r="E154" s="37"/>
@@ -10964,15 +11046,15 @@
       <c r="BR154"/>
     </row>
     <row r="155" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="193">
+      <c r="A155">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B155,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>7</v>
       </c>
       <c r="B155" s="175" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C155" s="170" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D155" s="36"/>
       <c r="E155" s="37"/>
@@ -11063,15 +11145,15 @@
       <c r="BR155"/>
     </row>
     <row r="156" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="193">
+      <c r="A156">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B156,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>7</v>
       </c>
       <c r="B156" s="175" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C156" s="170" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D156" s="36"/>
       <c r="E156" s="37"/>
@@ -11162,15 +11244,15 @@
       <c r="BR156"/>
     </row>
     <row r="157" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="193">
+      <c r="A157">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B157,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>7</v>
       </c>
       <c r="B157" s="175" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C157" s="170" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D157" s="36"/>
       <c r="E157" s="37"/>
@@ -11261,13 +11343,13 @@
       <c r="BR157"/>
     </row>
     <row r="158" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="193" t="str">
+      <c r="A158" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B158,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B158" s="175"/>
       <c r="C158" s="170" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D158" s="36"/>
       <c r="E158" s="37"/>
@@ -11358,13 +11440,13 @@
       <c r="BR158"/>
     </row>
     <row r="159" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="193" t="str">
+      <c r="A159" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B159,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B159" s="175"/>
       <c r="C159" s="170" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D159" s="36"/>
       <c r="E159" s="37"/>
@@ -11455,13 +11537,13 @@
       <c r="BR159"/>
     </row>
     <row r="160" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="193" t="str">
+      <c r="A160" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B160,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B160" s="175"/>
       <c r="C160" s="170" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D160" s="36"/>
       <c r="E160" s="37"/>
@@ -11552,15 +11634,15 @@
       <c r="BR160"/>
     </row>
     <row r="161" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="193">
+      <c r="A161">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B161,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>7</v>
       </c>
       <c r="B161" s="175" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C161" s="170" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D161" s="36"/>
       <c r="E161" s="37"/>
@@ -11651,15 +11733,15 @@
       <c r="BR161"/>
     </row>
     <row r="162" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="193">
+      <c r="A162">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B162,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>7</v>
       </c>
       <c r="B162" s="175" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C162" s="170" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D162" s="36"/>
       <c r="E162" s="37"/>
@@ -11750,13 +11832,13 @@
       <c r="BR162"/>
     </row>
     <row r="163" spans="1:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="193" t="str">
+      <c r="A163" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B163,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B163" s="175"/>
       <c r="C163" s="170" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D163" s="36"/>
       <c r="E163" s="37"/>
@@ -11847,15 +11929,15 @@
       <c r="BR163"/>
     </row>
     <row r="164" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A164" s="193">
+      <c r="A164">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B164,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>8</v>
       </c>
       <c r="B164" s="180" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C164" s="170" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D164" s="36"/>
       <c r="E164" s="37"/>
@@ -11890,13 +11972,13 @@
       </c>
     </row>
     <row r="165" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A165" s="193" t="str">
+      <c r="A165" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B165,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B165" s="175"/>
       <c r="C165" s="170" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D165" s="36"/>
       <c r="E165" s="37"/>
@@ -11931,15 +12013,15 @@
       </c>
     </row>
     <row r="166" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A166" s="193">
+      <c r="A166">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B166,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>3</v>
       </c>
       <c r="B166" s="174" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C166" s="170" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D166" s="36"/>
       <c r="E166" s="37"/>
@@ -11974,7 +12056,7 @@
       </c>
     </row>
     <row r="167" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A167" s="193">
+      <c r="A167">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B167,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>1</v>
       </c>
@@ -11982,7 +12064,7 @@
         <v>2</v>
       </c>
       <c r="C167" s="170" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D167" s="36"/>
       <c r="E167" s="37"/>
@@ -12017,15 +12099,15 @@
       </c>
     </row>
     <row r="168" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A168" s="193" t="str">
+      <c r="A168" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B168,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B168" s="175" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C168" s="170" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D168" s="36"/>
       <c r="E168" s="37"/>
@@ -12052,15 +12134,15 @@
       </c>
     </row>
     <row r="169" spans="1:70" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="193">
+      <c r="A169">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B169,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v>4</v>
       </c>
       <c r="B169" s="175" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C169" s="170" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D169" s="36"/>
       <c r="E169" s="37"/>
@@ -12095,13 +12177,13 @@
       </c>
     </row>
     <row r="170" spans="1:70" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="193" t="str">
+      <c r="A170" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B170,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B170" s="175"/>
       <c r="C170" s="181" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D170" s="36"/>
       <c r="E170" s="37"/>
@@ -12136,13 +12218,13 @@
       </c>
     </row>
     <row r="171" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A171" s="193" t="str">
+      <c r="A171" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B171,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B171" s="175"/>
       <c r="C171" s="170" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D171" s="36"/>
       <c r="E171" s="37"/>
@@ -12177,13 +12259,13 @@
       </c>
     </row>
     <row r="172" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A172" s="193" t="str">
+      <c r="A172" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B172,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B172" s="175"/>
       <c r="C172" s="170" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D172" s="36"/>
       <c r="E172" s="37"/>
@@ -12218,13 +12300,13 @@
       </c>
     </row>
     <row r="173" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A173" s="193" t="str">
+      <c r="A173" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B173,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="B173" s="175"/>
       <c r="C173" s="170" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D173" s="36"/>
       <c r="E173" s="37"/>
@@ -12259,12 +12341,12 @@
       </c>
     </row>
     <row r="174" spans="1:70" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="193" t="str">
+      <c r="A174" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Sheet1!B174,Sheet2!$A$2:$A$9,Sheet2!$B$2:$B$9),"")</f>
         <v/>
       </c>
       <c r="C174" s="182" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D174" s="44"/>
       <c r="E174" s="45"/>
@@ -12321,10 +12403,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -12345,7 +12427,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -12353,7 +12435,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -12361,7 +12443,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -12369,7 +12451,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -12377,7 +12459,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -12385,10 +12467,546 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B9">
         <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D077C35A-077A-F44E-B3BD-0C30C4418089}">
+  <dimension ref="A1:ET1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="5" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="22" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="33.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="29" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="27" bestFit="1" customWidth="1"/>
+    <col min="40" max="47" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="48" max="51" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="52" max="59" width="27" bestFit="1" customWidth="1"/>
+    <col min="60" max="67" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="68" max="69" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="70" max="71" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="75" max="76" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="78" max="79" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="80" max="81" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="82" max="84" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="85" max="86" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="87" max="89" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="14" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="34.83203125" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="36" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="14" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="105" max="106" width="19" bestFit="1" customWidth="1"/>
+    <col min="107" max="108" width="18" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="21" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="121" max="122" width="38" bestFit="1" customWidth="1"/>
+    <col min="123" max="124" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="125" max="126" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="127" max="128" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="129" max="130" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="131" max="133" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="134" max="136" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="138" max="138" width="22" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="140" max="141" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="142" max="143" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="144" max="144" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="145" max="145" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="146" max="146" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="147" max="149" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="40.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:150" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O1" t="s">
+        <v>152</v>
+      </c>
+      <c r="P1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>154</v>
+      </c>
+      <c r="R1" t="s">
+        <v>155</v>
+      </c>
+      <c r="S1" t="s">
+        <v>156</v>
+      </c>
+      <c r="T1" t="s">
+        <v>157</v>
+      </c>
+      <c r="U1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V1" t="s">
+        <v>159</v>
+      </c>
+      <c r="W1" s="193" t="s">
+        <v>26</v>
+      </c>
+      <c r="X1" s="193" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="193" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z1" s="193" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA1" s="193" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB1" s="193" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC1" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD1" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE1" s="193" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF1" s="194" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG1" s="194" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH1" s="194" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI1" s="194" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ1" s="194" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK1" s="194" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL1" s="194" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM1" s="194" t="s">
+        <v>41</v>
+      </c>
+      <c r="AN1" s="194" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO1" s="194" t="s">
+        <v>43</v>
+      </c>
+      <c r="AP1" s="194" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ1" s="194" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR1" s="194" t="s">
+        <v>46</v>
+      </c>
+      <c r="AS1" s="194" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT1" s="194" t="s">
+        <v>48</v>
+      </c>
+      <c r="AU1" s="194" t="s">
+        <v>49</v>
+      </c>
+      <c r="AV1" s="194" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW1" s="194" t="s">
+        <v>51</v>
+      </c>
+      <c r="AX1" s="194" t="s">
+        <v>52</v>
+      </c>
+      <c r="AY1" s="194" t="s">
+        <v>53</v>
+      </c>
+      <c r="AZ1" s="194" t="s">
+        <v>34</v>
+      </c>
+      <c r="BA1" s="194" t="s">
+        <v>35</v>
+      </c>
+      <c r="BB1" s="194" t="s">
+        <v>36</v>
+      </c>
+      <c r="BC1" s="194" t="s">
+        <v>37</v>
+      </c>
+      <c r="BD1" s="194" t="s">
+        <v>38</v>
+      </c>
+      <c r="BE1" s="194" t="s">
+        <v>39</v>
+      </c>
+      <c r="BF1" s="194" t="s">
+        <v>40</v>
+      </c>
+      <c r="BG1" s="194" t="s">
+        <v>41</v>
+      </c>
+      <c r="BH1" s="194" t="s">
+        <v>42</v>
+      </c>
+      <c r="BI1" s="194" t="s">
+        <v>43</v>
+      </c>
+      <c r="BJ1" s="194" t="s">
+        <v>44</v>
+      </c>
+      <c r="BK1" s="194" t="s">
+        <v>45</v>
+      </c>
+      <c r="BL1" s="194" t="s">
+        <v>46</v>
+      </c>
+      <c r="BM1" s="194" t="s">
+        <v>47</v>
+      </c>
+      <c r="BN1" s="194" t="s">
+        <v>48</v>
+      </c>
+      <c r="BO1" s="194" t="s">
+        <v>49</v>
+      </c>
+      <c r="BP1" s="194" t="s">
+        <v>52</v>
+      </c>
+      <c r="BQ1" s="194" t="s">
+        <v>53</v>
+      </c>
+      <c r="BR1" s="194" t="s">
+        <v>56</v>
+      </c>
+      <c r="BS1" s="194" t="s">
+        <v>56</v>
+      </c>
+      <c r="BT1" s="194" t="s">
+        <v>57</v>
+      </c>
+      <c r="BU1" s="194" t="s">
+        <v>58</v>
+      </c>
+      <c r="BV1" s="194" t="s">
+        <v>59</v>
+      </c>
+      <c r="BW1" s="194" t="s">
+        <v>60</v>
+      </c>
+      <c r="BX1" s="194" t="s">
+        <v>60</v>
+      </c>
+      <c r="BY1" s="194" t="s">
+        <v>61</v>
+      </c>
+      <c r="BZ1" s="194" t="s">
+        <v>62</v>
+      </c>
+      <c r="CA1" s="194" t="s">
+        <v>63</v>
+      </c>
+      <c r="CB1" s="194" t="s">
+        <v>64</v>
+      </c>
+      <c r="CC1" s="194" t="s">
+        <v>64</v>
+      </c>
+      <c r="CD1" s="194" t="s">
+        <v>66</v>
+      </c>
+      <c r="CE1" s="194" t="s">
+        <v>67</v>
+      </c>
+      <c r="CF1" s="194" t="s">
+        <v>68</v>
+      </c>
+      <c r="CG1" s="194" t="s">
+        <v>69</v>
+      </c>
+      <c r="CH1" s="194" t="s">
+        <v>70</v>
+      </c>
+      <c r="CI1" s="195" t="s">
+        <v>66</v>
+      </c>
+      <c r="CJ1" s="195" t="s">
+        <v>67</v>
+      </c>
+      <c r="CK1" s="195" t="s">
+        <v>68</v>
+      </c>
+      <c r="CL1" s="197" t="s">
+        <v>77</v>
+      </c>
+      <c r="CM1" s="197" t="s">
+        <v>78</v>
+      </c>
+      <c r="CN1" s="197" t="s">
+        <v>79</v>
+      </c>
+      <c r="CO1" s="197" t="s">
+        <v>162</v>
+      </c>
+      <c r="CP1" s="197" t="s">
+        <v>163</v>
+      </c>
+      <c r="CQ1" s="197" t="s">
+        <v>83</v>
+      </c>
+      <c r="CR1" s="197" t="s">
+        <v>84</v>
+      </c>
+      <c r="CS1" s="197" t="s">
+        <v>85</v>
+      </c>
+      <c r="CT1" s="197" t="s">
+        <v>86</v>
+      </c>
+      <c r="CU1" s="197" t="s">
+        <v>164</v>
+      </c>
+      <c r="CV1" s="197" t="s">
+        <v>88</v>
+      </c>
+      <c r="CW1" s="197" t="s">
+        <v>89</v>
+      </c>
+      <c r="CX1" s="197" t="s">
+        <v>90</v>
+      </c>
+      <c r="CY1" s="197" t="s">
+        <v>91</v>
+      </c>
+      <c r="CZ1" s="197" t="s">
+        <v>92</v>
+      </c>
+      <c r="DA1" s="199" t="s">
+        <v>93</v>
+      </c>
+      <c r="DB1" s="199" t="s">
+        <v>94</v>
+      </c>
+      <c r="DC1" s="199" t="s">
+        <v>95</v>
+      </c>
+      <c r="DD1" s="199" t="s">
+        <v>96</v>
+      </c>
+      <c r="DE1" s="199" t="s">
+        <v>97</v>
+      </c>
+      <c r="DF1" s="199" t="s">
+        <v>98</v>
+      </c>
+      <c r="DG1" s="199" t="s">
+        <v>99</v>
+      </c>
+      <c r="DH1" s="199" t="s">
+        <v>100</v>
+      </c>
+      <c r="DI1" s="199" t="s">
+        <v>160</v>
+      </c>
+      <c r="DJ1" s="196" t="s">
+        <v>102</v>
+      </c>
+      <c r="DK1" s="196" t="s">
+        <v>103</v>
+      </c>
+      <c r="DL1" s="196" t="s">
+        <v>102</v>
+      </c>
+      <c r="DM1" s="196" t="s">
+        <v>105</v>
+      </c>
+      <c r="DN1" s="196" t="s">
+        <v>161</v>
+      </c>
+      <c r="DO1" s="196" t="s">
+        <v>105</v>
+      </c>
+      <c r="DP1" s="196" t="s">
+        <v>108</v>
+      </c>
+      <c r="DQ1" s="196" t="s">
+        <v>109</v>
+      </c>
+      <c r="DR1" s="196" t="s">
+        <v>110</v>
+      </c>
+      <c r="DS1" s="196" t="s">
+        <v>112</v>
+      </c>
+      <c r="DT1" s="196" t="s">
+        <v>113</v>
+      </c>
+      <c r="DU1" s="196" t="s">
+        <v>114</v>
+      </c>
+      <c r="DV1" s="196" t="s">
+        <v>114</v>
+      </c>
+      <c r="DW1" s="196" t="s">
+        <v>115</v>
+      </c>
+      <c r="DX1" s="196" t="s">
+        <v>116</v>
+      </c>
+      <c r="DY1" s="196" t="s">
+        <v>117</v>
+      </c>
+      <c r="DZ1" s="196" t="s">
+        <v>117</v>
+      </c>
+      <c r="EA1" s="196" t="s">
+        <v>118</v>
+      </c>
+      <c r="EB1" s="196" t="s">
+        <v>119</v>
+      </c>
+      <c r="EC1" s="196" t="s">
+        <v>120</v>
+      </c>
+      <c r="ED1" s="196" t="s">
+        <v>121</v>
+      </c>
+      <c r="EE1" s="196" t="s">
+        <v>122</v>
+      </c>
+      <c r="EF1" s="196" t="s">
+        <v>123</v>
+      </c>
+      <c r="EG1" s="196" t="s">
+        <v>124</v>
+      </c>
+      <c r="EH1" s="196" t="s">
+        <v>125</v>
+      </c>
+      <c r="EI1" s="196" t="s">
+        <v>126</v>
+      </c>
+      <c r="EJ1" s="196" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK1" s="196" t="s">
+        <v>129</v>
+      </c>
+      <c r="EL1" s="196" t="s">
+        <v>130</v>
+      </c>
+      <c r="EM1" s="196" t="s">
+        <v>130</v>
+      </c>
+      <c r="EN1" s="196" t="s">
+        <v>132</v>
+      </c>
+      <c r="EO1" s="196" t="s">
+        <v>133</v>
+      </c>
+      <c r="EP1" s="200" t="s">
+        <v>134</v>
+      </c>
+      <c r="EQ1" s="200" t="s">
+        <v>135</v>
+      </c>
+      <c r="ER1" s="200" t="s">
+        <v>136</v>
+      </c>
+      <c r="ES1" s="200" t="s">
+        <v>137</v>
+      </c>
+      <c r="ET1" s="200" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
